--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F633"/>
+  <dimension ref="A1:F635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15610,6 +15610,54 @@
         <v>367.44</v>
       </c>
       <c r="F633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>371.18</v>
+      </c>
+      <c r="C634" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="D634" t="n">
+        <v>378.29</v>
+      </c>
+      <c r="E634" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>371.53</v>
+      </c>
+      <c r="C635" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="D635" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="E635" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="F635" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15626,7 +15674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B686"/>
+  <dimension ref="A1:B688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22489,6 +22537,26 @@
       </c>
       <c r="B686" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -22657,28 +22725,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1229600323227834</v>
+        <v>-0.125896886123104</v>
       </c>
       <c r="J2" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04481758808801728</v>
+        <v>0.04702640910630818</v>
       </c>
       <c r="M2" t="n">
-        <v>3.196719109562904</v>
+        <v>3.201086214125776</v>
       </c>
       <c r="N2" t="n">
-        <v>17.85517483118379</v>
+        <v>17.8665645629341</v>
       </c>
       <c r="O2" t="n">
-        <v>4.225538407254605</v>
+        <v>4.226885917899145</v>
       </c>
       <c r="P2" t="n">
-        <v>379.2350973177472</v>
+        <v>379.2650326000756</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22739,28 +22807,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01353687872917509</v>
+        <v>0.01213842299731965</v>
       </c>
       <c r="J3" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00161407441159156</v>
+        <v>0.001304102044603739</v>
       </c>
       <c r="M3" t="n">
-        <v>2.062232371491538</v>
+        <v>2.062965803186896</v>
       </c>
       <c r="N3" t="n">
-        <v>6.271875019003833</v>
+        <v>6.267714195094691</v>
       </c>
       <c r="O3" t="n">
-        <v>2.504371182353732</v>
+        <v>2.503540332228481</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4226466510166</v>
+        <v>373.4369080171805</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22821,28 +22889,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07387982112382965</v>
+        <v>-0.07509244699201049</v>
       </c>
       <c r="J4" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K4" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03029199154965256</v>
+        <v>0.03144061693572742</v>
       </c>
       <c r="M4" t="n">
-        <v>2.459889720671009</v>
+        <v>2.458189766530838</v>
       </c>
       <c r="N4" t="n">
-        <v>9.641292360308702</v>
+        <v>9.622399351158647</v>
       </c>
       <c r="O4" t="n">
-        <v>3.105043052891328</v>
+        <v>3.101999250670227</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2691578905565</v>
+        <v>382.281535448807</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22903,28 +22971,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1524743513161577</v>
+        <v>-0.1547182377424548</v>
       </c>
       <c r="J5" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K5" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1380557025975004</v>
+        <v>0.1418272349922444</v>
       </c>
       <c r="M5" t="n">
-        <v>2.251790465798451</v>
+        <v>2.254736910834991</v>
       </c>
       <c r="N5" t="n">
-        <v>7.998099611420167</v>
+        <v>8.012270216596804</v>
       </c>
       <c r="O5" t="n">
-        <v>2.828091160380119</v>
+        <v>2.830595381999484</v>
       </c>
       <c r="P5" t="n">
-        <v>373.5878601390312</v>
+        <v>373.6107743483799</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22966,7 +23034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F633"/>
+  <dimension ref="A1:F635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43193,6 +43261,70 @@
         </is>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.55172042863074,174.70982898851057</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.552438600150815,174.70986634005234</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.55313800726836,174.71001387498262</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.55385661357733,174.71007763427488</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.551720287740245,174.70983289428415</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.55243902207996,174.7098590980171</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.55313764526917,174.71001651813907</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.553856232994654,174.7100795889036</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F635"/>
+  <dimension ref="A1:F636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15658,6 +15658,30 @@
         <v>366.12</v>
       </c>
       <c r="F635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>373.93</v>
+      </c>
+      <c r="C636" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="D636" t="n">
+        <v>379</v>
+      </c>
+      <c r="E636" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="F636" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15674,7 +15698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B688"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22557,6 +22581,16 @@
       </c>
       <c r="B688" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -22725,28 +22759,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.125896886123104</v>
+        <v>-0.1265350698248042</v>
       </c>
       <c r="J2" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K2" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04702640910630818</v>
+        <v>0.04762566112448907</v>
       </c>
       <c r="M2" t="n">
-        <v>3.201086214125776</v>
+        <v>3.199136266104062</v>
       </c>
       <c r="N2" t="n">
-        <v>17.8665645629341</v>
+        <v>17.84465474226487</v>
       </c>
       <c r="O2" t="n">
-        <v>4.226885917899145</v>
+        <v>4.224293401536507</v>
       </c>
       <c r="P2" t="n">
-        <v>379.2650326000756</v>
+        <v>379.2715632036025</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22807,28 +22841,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01213842299731965</v>
+        <v>0.01129615993543628</v>
       </c>
       <c r="J3" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K3" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001304102044603739</v>
+        <v>0.001131589572461733</v>
       </c>
       <c r="M3" t="n">
-        <v>2.062965803186896</v>
+        <v>2.064091331187943</v>
       </c>
       <c r="N3" t="n">
-        <v>6.267714195094691</v>
+        <v>6.268931460525502</v>
       </c>
       <c r="O3" t="n">
-        <v>2.503540332228481</v>
+        <v>2.503783429237741</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4369080171805</v>
+        <v>373.4455309980448</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22889,28 +22923,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07509244699201049</v>
+        <v>-0.07550621773122246</v>
       </c>
       <c r="J4" t="n">
+        <v>635</v>
+      </c>
+      <c r="K4" t="n">
         <v>634</v>
       </c>
-      <c r="K4" t="n">
-        <v>633</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03144061693572742</v>
+        <v>0.03187762421320295</v>
       </c>
       <c r="M4" t="n">
-        <v>2.458189766530838</v>
+        <v>2.456405565703233</v>
       </c>
       <c r="N4" t="n">
-        <v>9.622399351158647</v>
+        <v>9.609898878980255</v>
       </c>
       <c r="O4" t="n">
-        <v>3.101999250670227</v>
+        <v>3.0999836901152</v>
       </c>
       <c r="P4" t="n">
-        <v>382.281535448807</v>
+        <v>382.285775411003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22971,28 +23005,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1547182377424548</v>
+        <v>-0.1553676286652771</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1418272349922444</v>
+        <v>0.1431836395691655</v>
       </c>
       <c r="M5" t="n">
-        <v>2.254736910834991</v>
+        <v>2.254108607985065</v>
       </c>
       <c r="N5" t="n">
-        <v>8.012270216596804</v>
+        <v>8.00623321212152</v>
       </c>
       <c r="O5" t="n">
-        <v>2.830595381999484</v>
+        <v>2.82952879683553</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6107743483799</v>
+        <v>373.6174316605945</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -23034,7 +23068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F635"/>
+  <dimension ref="A1:F636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43325,6 +43359,38 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.55171932163066,174.70985967673093</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.55243911295696,174.7098575381941</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.5531369363539,174.71002169432035</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.55385335747995,174.71009435720865</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F636"/>
+  <dimension ref="A1:F637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15682,6 +15682,30 @@
         <v>367.48</v>
       </c>
       <c r="F636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="C637" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="D637" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="E637" t="n">
+        <v>365.42</v>
+      </c>
+      <c r="F637" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15698,7 +15722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22591,6 +22615,16 @@
       </c>
       <c r="B689" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -22759,34 +22793,30 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1265350698248042</v>
+        <v>-0.1275609657129214</v>
       </c>
       <c r="J2" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04762566112448907</v>
+        <v>0.04848554723432863</v>
       </c>
       <c r="M2" t="n">
-        <v>3.199136266104062</v>
+        <v>3.199109849034334</v>
       </c>
       <c r="N2" t="n">
-        <v>17.84465474226487</v>
+        <v>17.83285542509556</v>
       </c>
       <c r="O2" t="n">
-        <v>4.224293401536507</v>
+        <v>4.222896568126616</v>
       </c>
       <c r="P2" t="n">
-        <v>379.2715632036025</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.2821013907162</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.70568684897657 -36.55186977315394, 174.71597173012387 -36.551498686807356)</t>
@@ -22841,34 +22871,30 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01129615993543628</v>
+        <v>0.009964870904701072</v>
       </c>
       <c r="J3" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001131589572461733</v>
+        <v>0.0008800726114733814</v>
       </c>
       <c r="M3" t="n">
-        <v>2.064091331187943</v>
+        <v>2.067763420550532</v>
       </c>
       <c r="N3" t="n">
-        <v>6.268931460525502</v>
+        <v>6.286652330200377</v>
       </c>
       <c r="O3" t="n">
-        <v>2.503783429237741</v>
+        <v>2.50731975029121</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4455309980448</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>373.4592124679756</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.7057228773967 -36.552679930472195, 174.7159913061154 -36.552081593846225)</t>
@@ -22923,34 +22949,30 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07550621773122246</v>
+        <v>-0.07581173261531103</v>
       </c>
       <c r="J4" t="n">
+        <v>636</v>
+      </c>
+      <c r="K4" t="n">
         <v>635</v>
       </c>
-      <c r="K4" t="n">
-        <v>634</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03187762421320295</v>
+        <v>0.03223446274795183</v>
       </c>
       <c r="M4" t="n">
-        <v>2.456405565703233</v>
+        <v>2.454070254364187</v>
       </c>
       <c r="N4" t="n">
-        <v>9.609898878980255</v>
+        <v>9.596214422528396</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0999836901152</v>
+        <v>3.097775721792718</v>
       </c>
       <c r="P4" t="n">
-        <v>382.285775411003</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>382.2889179223583</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.7058476762814 -36.553708521324566, 174.715997345988 -36.552318370074616)</t>
@@ -23005,34 +23027,30 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1553676286652771</v>
+        <v>-0.1566664909815157</v>
       </c>
       <c r="J5" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K5" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1431836395691655</v>
+        <v>0.1452772523293566</v>
       </c>
       <c r="M5" t="n">
-        <v>2.254108607985065</v>
+        <v>2.256388530416781</v>
       </c>
       <c r="N5" t="n">
-        <v>8.00623321212152</v>
+        <v>8.019788653859813</v>
       </c>
       <c r="O5" t="n">
-        <v>2.82952879683553</v>
+        <v>2.831923136997156</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6174316605945</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>373.6307974281283</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.7061038319682 -36.554630272894435, 174.71611103062818 -36.55268169111079)</t>
@@ -23068,7 +23086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F636"/>
+  <dimension ref="A1:F637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43391,6 +43409,38 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.55171982078803,174.70984583913352</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.552440119093696,174.70984026872497</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.55313643860476,174.71002532866032</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.553857713038276,174.71007198756965</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F637"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15708,6 +15708,78 @@
       <c r="F637" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="C638" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="D638" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="E638" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="C639" t="n">
+        <v>371.78</v>
+      </c>
+      <c r="D639" t="n">
+        <v>379.46</v>
+      </c>
+      <c r="E639" t="n">
+        <v>366.18</v>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="C640" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="D640" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="E640" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B690"/>
+  <dimension ref="A1:B693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22625,6 +22697,36 @@
       </c>
       <c r="B690" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -22793,28 +22895,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1275609657129214</v>
+        <v>-0.130217213285072</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K2" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04848554723432863</v>
+        <v>0.05082997006238188</v>
       </c>
       <c r="M2" t="n">
-        <v>3.199109849034334</v>
+        <v>3.197195897622429</v>
       </c>
       <c r="N2" t="n">
-        <v>17.83285542509556</v>
+        <v>17.78780834988535</v>
       </c>
       <c r="O2" t="n">
-        <v>4.222896568126616</v>
+        <v>4.217559525351758</v>
       </c>
       <c r="P2" t="n">
-        <v>379.2821013907162</v>
+        <v>379.3094438368606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22871,28 +22973,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009964870904701072</v>
+        <v>0.007981020419550492</v>
       </c>
       <c r="J3" t="n">
+        <v>639</v>
+      </c>
+      <c r="K3" t="n">
         <v>636</v>
       </c>
-      <c r="K3" t="n">
-        <v>633</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0008800726114733814</v>
+        <v>0.0005685114359095245</v>
       </c>
       <c r="M3" t="n">
-        <v>2.067763420550532</v>
+        <v>2.068351845778445</v>
       </c>
       <c r="N3" t="n">
-        <v>6.286652330200377</v>
+        <v>6.281923790519733</v>
       </c>
       <c r="O3" t="n">
-        <v>2.50731975029121</v>
+        <v>2.506376625832545</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4592124679756</v>
+        <v>373.4796363570443</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22949,28 +23051,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07581173261531103</v>
+        <v>-0.07701004249463804</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K4" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03223446274795183</v>
+        <v>0.03354549839538301</v>
       </c>
       <c r="M4" t="n">
-        <v>2.454070254364187</v>
+        <v>2.448507161270151</v>
       </c>
       <c r="N4" t="n">
-        <v>9.596214422528396</v>
+        <v>9.559073585524374</v>
       </c>
       <c r="O4" t="n">
-        <v>3.097775721792718</v>
+        <v>3.091775151191363</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2889179223583</v>
+        <v>382.3012766274227</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23027,28 +23129,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1566664909815157</v>
+        <v>-0.1599858249596703</v>
       </c>
       <c r="J5" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K5" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1452772523293566</v>
+        <v>0.1509975768321</v>
       </c>
       <c r="M5" t="n">
-        <v>2.256388530416781</v>
+        <v>2.260589976837101</v>
       </c>
       <c r="N5" t="n">
-        <v>8.019788653859813</v>
+        <v>8.040578689913479</v>
       </c>
       <c r="O5" t="n">
-        <v>2.831923136997156</v>
+        <v>2.835591418013794</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6307974281283</v>
+        <v>373.6650316855847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23086,7 +23188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F637"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43441,6 +43543,102 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.551720001933454,174.70984081742475</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.552439586815225,174.70984940483126</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.553137102270256,174.71002048287366</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.55385803019041,174.71007035871233</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.55171965574424,174.70985041446818</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.552438671554235,174.70986511447714</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.553136242521724,174.71002676037</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.55385610613374,174.71008024044647</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.551719333707055,174.70985934195033</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.5524380808528,174.70987525332637</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.55313743410293,174.7100180599803</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.55385561983357,174.71008273802755</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F640"/>
+  <dimension ref="A1:F647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15778,6 +15778,174 @@
         <v>366.41</v>
       </c>
       <c r="F640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>377.26</v>
+      </c>
+      <c r="C641" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="D641" t="n">
+        <v>378.61</v>
+      </c>
+      <c r="E641" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>377.08</v>
+      </c>
+      <c r="C642" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="D642" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="E642" t="n">
+        <v>366.59</v>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="C643" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="D643" t="n">
+        <v>378.48</v>
+      </c>
+      <c r="E643" t="n">
+        <v>366.46</v>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="C644" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="D644" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="E644" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="C645" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="D645" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="E645" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="C646" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="D646" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="E646" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="C647" t="n">
+        <v>373.31</v>
+      </c>
+      <c r="D647" t="n">
+        <v>380.08</v>
+      </c>
+      <c r="E647" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="F647" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15794,7 +15962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22727,6 +22895,76 @@
       </c>
       <c r="B693" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -22895,28 +23133,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.130217213285072</v>
+        <v>-0.1260217426571479</v>
       </c>
       <c r="J2" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05082997006238188</v>
+        <v>0.04879273685494212</v>
       </c>
       <c r="M2" t="n">
-        <v>3.197195897622429</v>
+        <v>3.183177474599242</v>
       </c>
       <c r="N2" t="n">
-        <v>17.78780834988535</v>
+        <v>17.63659927776005</v>
       </c>
       <c r="O2" t="n">
-        <v>4.217559525351758</v>
+        <v>4.19959513260029</v>
       </c>
       <c r="P2" t="n">
-        <v>379.3094438368606</v>
+        <v>379.2658932703332</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22973,28 +23211,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007981020419550492</v>
+        <v>0.006755852288618363</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="K3" t="n">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005685114359095245</v>
+        <v>0.0004174213325112142</v>
       </c>
       <c r="M3" t="n">
-        <v>2.068351845778445</v>
+        <v>2.052060043984686</v>
       </c>
       <c r="N3" t="n">
-        <v>6.281923790519733</v>
+        <v>6.217589619521425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.506376625832545</v>
+        <v>2.493509498582555</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4796363570443</v>
+        <v>373.492358922398</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23051,28 +23289,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07701004249463804</v>
+        <v>-0.07921717195515421</v>
       </c>
       <c r="J4" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03354549839538301</v>
+        <v>0.03623491835989867</v>
       </c>
       <c r="M4" t="n">
-        <v>2.448507161270151</v>
+        <v>2.43284662963608</v>
       </c>
       <c r="N4" t="n">
-        <v>9.559073585524374</v>
+        <v>9.469757913426413</v>
       </c>
       <c r="O4" t="n">
-        <v>3.091775151191363</v>
+        <v>3.077297176651357</v>
       </c>
       <c r="P4" t="n">
-        <v>382.3012766274227</v>
+        <v>382.3241955174109</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23129,28 +23367,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1599858249596703</v>
+        <v>-0.1635871572800876</v>
       </c>
       <c r="J5" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1509975768321</v>
+        <v>0.1593805578354007</v>
       </c>
       <c r="M5" t="n">
-        <v>2.260589976837101</v>
+        <v>2.25181779074325</v>
       </c>
       <c r="N5" t="n">
-        <v>8.040578689913479</v>
+        <v>7.997303836909056</v>
       </c>
       <c r="O5" t="n">
-        <v>2.835591418013794</v>
+        <v>2.827950465780661</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6650316855847</v>
+        <v>373.7024376684904</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23188,7 +23426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F640"/>
+  <dimension ref="A1:F647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43639,6 +43877,230 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.551717981143646,174.7098968373743</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.55243761348402,174.7098832752729</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.553137524602754,174.7100173991912</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.5538561484207,174.71008002326553</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.551718053602706,174.70989482869092</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.55243765892268,174.7098824953614</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.55313717768677,174.71001993221608</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.5538552392508,174.7100846926562</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.55171792478659,174.7098983996836</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.55243774330873,174.70988104695442</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.55313772068567,174.7100159674815</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.553855514116144,174.71008328097997</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.55171759872031,174.70990743875873</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.552438093835256,174.70987503049454</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.55313664977107,174.7100237868191</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.55385139113431,174.71010445612245</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.551717715460164,174.70990420254665</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.552437944536955,174.70987759306078</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.55313594085549,174.71002896300024</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.553850270528336,174.7101102114172</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.55171742159761,174.7099123488736</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.552437853659704,174.70987915288373</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.55313592577218,174.71002907313175</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.553850693398545,174.7101080396079</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.551717719485666,174.70990409095313</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.55243767839637,174.70988216111365</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.55313530735629,174.71003358852371</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.55385065111153,174.71010825678883</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F647"/>
+  <dimension ref="A1:F651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15946,6 +15946,102 @@
         <v>368.76</v>
       </c>
       <c r="F647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="C648" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="D648" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="E648" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>381.37</v>
+      </c>
+      <c r="C649" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="D649" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="E649" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="C650" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="D650" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="E650" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="C651" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="D651" t="n">
+        <v>382.19</v>
+      </c>
+      <c r="E651" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="F651" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15962,7 +16058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22965,6 +23061,46 @@
       </c>
       <c r="B700" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -23133,28 +23269,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1260217426571479</v>
+        <v>-0.1198303190031456</v>
       </c>
       <c r="J2" t="n">
+        <v>650</v>
+      </c>
+      <c r="K2" t="n">
         <v>646</v>
       </c>
-      <c r="K2" t="n">
-        <v>642</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04879273685494212</v>
+        <v>0.04453289207065014</v>
       </c>
       <c r="M2" t="n">
-        <v>3.183177474599242</v>
+        <v>3.194510223283073</v>
       </c>
       <c r="N2" t="n">
-        <v>17.63659927776005</v>
+        <v>17.68628897634122</v>
       </c>
       <c r="O2" t="n">
-        <v>4.19959513260029</v>
+        <v>4.205506982082092</v>
       </c>
       <c r="P2" t="n">
-        <v>379.2658932703332</v>
+        <v>379.201352377705</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23211,28 +23347,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006755852288618363</v>
+        <v>0.01003334984085291</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004174213325112142</v>
+        <v>0.000926553112779116</v>
       </c>
       <c r="M3" t="n">
-        <v>2.052060043984686</v>
+        <v>2.055582637596982</v>
       </c>
       <c r="N3" t="n">
-        <v>6.217589619521425</v>
+        <v>6.22312890890709</v>
       </c>
       <c r="O3" t="n">
-        <v>2.493509498582555</v>
+        <v>2.494619992886109</v>
       </c>
       <c r="P3" t="n">
-        <v>373.492358922398</v>
+        <v>373.4581792562039</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23289,28 +23425,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07921717195515421</v>
+        <v>-0.07718449797516652</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03623491835989867</v>
+        <v>0.0348683806266854</v>
       </c>
       <c r="M4" t="n">
-        <v>2.43284662963608</v>
+        <v>2.428096255207484</v>
       </c>
       <c r="N4" t="n">
-        <v>9.469757913426413</v>
+        <v>9.428842615109927</v>
       </c>
       <c r="O4" t="n">
-        <v>3.077297176651357</v>
+        <v>3.070642052586059</v>
       </c>
       <c r="P4" t="n">
-        <v>382.3241955174109</v>
+        <v>382.3029784475394</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23367,28 +23503,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1635871572800876</v>
+        <v>-0.1624974251413243</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="K5" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1593805578354007</v>
+        <v>0.1593818618615848</v>
       </c>
       <c r="M5" t="n">
-        <v>2.25181779074325</v>
+        <v>2.244039239476702</v>
       </c>
       <c r="N5" t="n">
-        <v>7.997303836909056</v>
+        <v>7.95295678320087</v>
       </c>
       <c r="O5" t="n">
-        <v>2.827950465780661</v>
+        <v>2.820098718697782</v>
       </c>
       <c r="P5" t="n">
-        <v>373.7024376684904</v>
+        <v>373.6910601533392</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23426,7 +23562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F647"/>
+  <dimension ref="A1:F651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44101,6 +44237,134 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.5517168821772,174.70992730240496</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.55243577645984,174.70991480597814</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.55313345210758,174.71004713469912</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.55384779673685,174.71012291650115</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.551716326652766,174.70994270231012</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.55243580891618,174.70991424889854</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.55313247169097,174.7100542932468</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.5538473104358,174.71012541408166</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.551716234065154,174.70994526896095</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.55243551031784,174.7099193740307</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.55313239627429,174.71005484390432</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.55384747958399,174.710124545358</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.55171651182779,174.70993756900845</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.552435692073374,174.70991625438504</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.55313212477423,174.71005682627134</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.55384773330629,174.71012324227254</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
